--- a/DATA/Processed/residual_diagnostics/Thailand_residuals.xlsx
+++ b/DATA/Processed/residual_diagnostics/Thailand_residuals.xlsx
@@ -442,10 +442,10 @@
         <v>42217</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.001029181943143611</v>
+        <v>-0.0006031500776501345</v>
       </c>
       <c r="C2" t="n">
-        <v>1.059215472092859e-06</v>
+        <v>3.637900161693632e-07</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>42248</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006163026647693129</v>
+        <v>0.0001481311451934704</v>
       </c>
       <c r="C3" t="n">
-        <v>3.798289746017562e-07</v>
+        <v>2.1942836176329e-08</v>
       </c>
     </row>
     <row r="4">
@@ -464,10 +464,10 @@
         <v>42278</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001750203025679382</v>
+        <v>0.001658904403645535</v>
       </c>
       <c r="C4" t="n">
-        <v>3.063210631097265e-06</v>
+        <v>2.751963820434548e-06</v>
       </c>
     </row>
     <row r="5">
@@ -475,10 +475,10 @@
         <v>42309</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.001977292882389608</v>
+        <v>-0.001882985727175269</v>
       </c>
       <c r="C5" t="n">
-        <v>3.909687142748604e-06</v>
+        <v>3.545635248745776e-06</v>
       </c>
     </row>
     <row r="6">
@@ -486,10 +486,10 @@
         <v>42339</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0008322802976385327</v>
+        <v>-0.0009311308838719943</v>
       </c>
       <c r="C6" t="n">
-        <v>6.926904938372845e-07</v>
+        <v>8.670047229002413e-07</v>
       </c>
     </row>
     <row r="7">
@@ -497,10 +497,10 @@
         <v>42370</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0005739089486845794</v>
+        <v>-0.0001284186021314865</v>
       </c>
       <c r="C7" t="n">
-        <v>3.293714813802392e-07</v>
+        <v>1.649133737340504e-08</v>
       </c>
     </row>
     <row r="8">
@@ -508,10 +508,10 @@
         <v>42401</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000846121889361879</v>
+        <v>0.0005384207303194826</v>
       </c>
       <c r="C8" t="n">
-        <v>7.159222516573158e-07</v>
+        <v>2.89896882837765e-07</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +519,10 @@
         <v>42430</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0005610547727493897</v>
+        <v>0.001129932102723265</v>
       </c>
       <c r="C9" t="n">
-        <v>3.147824580248694e-07</v>
+        <v>1.276746556764619e-06</v>
       </c>
     </row>
     <row r="10">
@@ -530,10 +530,10 @@
         <v>42461</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00196195319611517</v>
+        <v>0.002433223515090246</v>
       </c>
       <c r="C10" t="n">
-        <v>3.849260343746532e-06</v>
+        <v>5.92057667438813e-06</v>
       </c>
     </row>
     <row r="11">
@@ -541,10 +541,10 @@
         <v>42491</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002251642629938366</v>
+        <v>0.001940199122054819</v>
       </c>
       <c r="C11" t="n">
-        <v>5.069894532955762e-06</v>
+        <v>3.764372633222292e-06</v>
       </c>
     </row>
     <row r="12">
@@ -552,10 +552,10 @@
         <v>42522</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.001089346543454882</v>
+        <v>-0.001855018119913657</v>
       </c>
       <c r="C12" t="n">
-        <v>1.186675891737098e-06</v>
+        <v>3.441092225207997e-06</v>
       </c>
     </row>
     <row r="13">
@@ -563,10 +563,10 @@
         <v>42552</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.001075968373065358</v>
+        <v>0.0005137475097968251</v>
       </c>
       <c r="C13" t="n">
-        <v>1.157707939836913e-06</v>
+        <v>2.63936503822439e-07</v>
       </c>
     </row>
     <row r="14">
@@ -574,10 +574,10 @@
         <v>42583</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0002152026597972389</v>
+        <v>-0.0009630863855060686</v>
       </c>
       <c r="C14" t="n">
-        <v>4.631218478380614e-08</v>
+        <v>9.275353859471438e-07</v>
       </c>
     </row>
     <row r="15">
@@ -585,10 +585,10 @@
         <v>42614</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.000165267261858913</v>
+        <v>-0.0001889655278571256</v>
       </c>
       <c r="C15" t="n">
-        <v>2.731326784234251e-08</v>
+        <v>3.570797071832212e-08</v>
       </c>
     </row>
     <row r="16">
@@ -596,10 +596,10 @@
         <v>42644</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001126189132744268</v>
+        <v>0.00134127879932176</v>
       </c>
       <c r="C16" t="n">
-        <v>1.268301962711287e-06</v>
+        <v>1.799028817510022e-06</v>
       </c>
     </row>
     <row r="17">
@@ -607,10 +607,10 @@
         <v>42675</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.000783613562881338</v>
+        <v>-0.001182357582409459</v>
       </c>
       <c r="C17" t="n">
-        <v>6.140502159315846e-07</v>
+        <v>1.397969452681141e-06</v>
       </c>
     </row>
     <row r="18">
@@ -618,10 +618,10 @@
         <v>42705</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0003920976157399036</v>
+        <v>-0.000549480800513697</v>
       </c>
       <c r="C18" t="n">
-        <v>1.537405402689171e-07</v>
+        <v>3.019291501331733e-07</v>
       </c>
     </row>
     <row r="19">
@@ -629,10 +629,10 @@
         <v>42736</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0001132753302492847</v>
+        <v>0.0007340085407248527</v>
       </c>
       <c r="C19" t="n">
-        <v>1.28313004430845e-08</v>
+        <v>5.387685378570277e-07</v>
       </c>
     </row>
     <row r="20">
@@ -640,10 +640,10 @@
         <v>42767</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0004096761357725914</v>
+        <v>-0.0003122588393407953</v>
       </c>
       <c r="C20" t="n">
-        <v>1.678345362215628e-07</v>
+        <v>9.750558274646061e-08</v>
       </c>
     </row>
     <row r="21">
@@ -651,10 +651,10 @@
         <v>42795</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.002265872561800818</v>
+        <v>-0.002179628832754392</v>
       </c>
       <c r="C21" t="n">
-        <v>5.134178466321804e-06</v>
+        <v>4.750781848574274e-06</v>
       </c>
     </row>
     <row r="22">
@@ -662,10 +662,10 @@
         <v>42826</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00123280069145043</v>
+        <v>0.001355040563038877</v>
       </c>
       <c r="C22" t="n">
-        <v>1.519797544840659e-06</v>
+        <v>1.836134927480716e-06</v>
       </c>
     </row>
     <row r="23">
@@ -673,10 +673,10 @@
         <v>42856</v>
       </c>
       <c r="B23" t="n">
-        <v>0.001056698892035393</v>
+        <v>0.0006087540022994467</v>
       </c>
       <c r="C23" t="n">
-        <v>1.116612548428828e-06</v>
+        <v>3.705814353155948e-07</v>
       </c>
     </row>
     <row r="24">
@@ -684,10 +684,10 @@
         <v>42887</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.0006014777056941375</v>
+        <v>-0.001369145109053891</v>
       </c>
       <c r="C24" t="n">
-        <v>3.617754304470834e-07</v>
+        <v>1.874558329646192e-06</v>
       </c>
     </row>
     <row r="25">
@@ -695,10 +695,10 @@
         <v>42917</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.001474057798964695</v>
+        <v>-0.0001065177498372636</v>
       </c>
       <c r="C25" t="n">
-        <v>2.172846394688642e-06</v>
+        <v>1.134603103039386e-08</v>
       </c>
     </row>
     <row r="26">
@@ -706,10 +706,10 @@
         <v>42948</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0006840178002716409</v>
+        <v>0.0003591734606350692</v>
       </c>
       <c r="C26" t="n">
-        <v>4.678803510884545e-07</v>
+        <v>1.290055748245716e-07</v>
       </c>
     </row>
     <row r="27">
@@ -717,10 +717,10 @@
         <v>42979</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0008887593649623078</v>
+        <v>0.0008461697856618723</v>
       </c>
       <c r="C27" t="n">
-        <v>7.898932088082046e-07</v>
+        <v>7.160033061670589e-07</v>
       </c>
     </row>
     <row r="28">
@@ -728,10 +728,10 @@
         <v>43009</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0001221003370352183</v>
+        <v>0.0002644900100157991</v>
       </c>
       <c r="C28" t="n">
-        <v>1.49084923041139e-08</v>
+        <v>6.995496539815751e-08</v>
       </c>
     </row>
     <row r="29">
@@ -739,10 +739,10 @@
         <v>43040</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.0004090175048784486</v>
+        <v>-0.0001994267989409996</v>
       </c>
       <c r="C29" t="n">
-        <v>1.672953192969917e-07</v>
+        <v>3.977104813585389e-08</v>
       </c>
     </row>
     <row r="30">
@@ -750,10 +750,10 @@
         <v>43070</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0001045972158307445</v>
+        <v>0.0002801718471946752</v>
       </c>
       <c r="C30" t="n">
-        <v>1.094057755954335e-08</v>
+        <v>7.849626396047643e-08</v>
       </c>
     </row>
     <row r="31">
@@ -761,10 +761,10 @@
         <v>43101</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.0003711348230771493</v>
+        <v>-0.0007876090820292539</v>
       </c>
       <c r="C31" t="n">
-        <v>1.377410569005069e-07</v>
+        <v>6.20328066094964e-07</v>
       </c>
     </row>
     <row r="32">
@@ -772,10 +772,10 @@
         <v>43132</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.001366030437618851</v>
+        <v>-0.0009238604350926621</v>
       </c>
       <c r="C32" t="n">
-        <v>1.86603915650115e-06</v>
+        <v>8.535181035296029e-07</v>
       </c>
     </row>
     <row r="33">
@@ -783,10 +783,10 @@
         <v>43160</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.0004239927494585245</v>
+        <v>-0.000601670814010606</v>
       </c>
       <c r="C33" t="n">
-        <v>1.797698515933991e-07</v>
+        <v>3.620077684321852e-07</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         <v>43191</v>
       </c>
       <c r="B34" t="n">
-        <v>0.001255234869805802</v>
+        <v>0.001031075155366254</v>
       </c>
       <c r="C34" t="n">
-        <v>1.575614578376389e-06</v>
+        <v>1.063115976013544e-06</v>
       </c>
     </row>
     <row r="35">
@@ -805,10 +805,10 @@
         <v>43221</v>
       </c>
       <c r="B35" t="n">
-        <v>0.001316155174253154</v>
+        <v>0.001114446708127325</v>
       </c>
       <c r="C35" t="n">
-        <v>1.732264442713352e-06</v>
+        <v>1.24199146525583e-06</v>
       </c>
     </row>
     <row r="36">
@@ -816,10 +816,10 @@
         <v>43252</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.001505762928793657</v>
+        <v>-0.00143378625752957</v>
       </c>
       <c r="C36" t="n">
-        <v>2.267321997729251e-06</v>
+        <v>2.05574303228065e-06</v>
       </c>
     </row>
     <row r="37">
@@ -827,10 +827,10 @@
         <v>43282</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.0002029901131582871</v>
+        <v>0.0002286315722296545</v>
       </c>
       <c r="C37" t="n">
-        <v>4.120498604001421e-08</v>
+        <v>5.227239582020371e-08</v>
       </c>
     </row>
     <row r="38">
@@ -838,10 +838,10 @@
         <v>43313</v>
       </c>
       <c r="B38" t="n">
-        <v>-7.31697937457938e-05</v>
+        <v>-0.0002054505757301415</v>
       </c>
       <c r="C38" t="n">
-        <v>5.353818716802006e-09</v>
+        <v>4.220993906784663e-08</v>
       </c>
     </row>
     <row r="39">
@@ -849,10 +849,10 @@
         <v>43344</v>
       </c>
       <c r="B39" t="n">
-        <v>0.001080472121977704</v>
+        <v>0.001177655969763679</v>
       </c>
       <c r="C39" t="n">
-        <v>1.167420006371002e-06</v>
+        <v>1.386873583120031e-06</v>
       </c>
     </row>
     <row r="40">
@@ -860,10 +860,10 @@
         <v>43374</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0001869620406295208</v>
+        <v>-5.699214476596724e-05</v>
       </c>
       <c r="C40" t="n">
-        <v>3.495480463635458e-08</v>
+        <v>3.248104565024967e-09</v>
       </c>
     </row>
     <row r="41">
@@ -871,10 +871,10 @@
         <v>43405</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.0009276911447931508</v>
+        <v>-0.001148928340871387</v>
       </c>
       <c r="C41" t="n">
-        <v>8.606108601276267e-07</v>
+        <v>1.320036332457478e-06</v>
       </c>
     </row>
     <row r="42">
@@ -882,10 +882,10 @@
         <v>43435</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.002184399942848322</v>
+        <v>-0.001519812543956508</v>
       </c>
       <c r="C42" t="n">
-        <v>4.771603110315754e-06</v>
+        <v>2.309830168767554e-06</v>
       </c>
     </row>
     <row r="43">
@@ -893,10 +893,10 @@
         <v>43466</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0002559170582156711</v>
+        <v>0.0001167249731225672</v>
       </c>
       <c r="C43" t="n">
-        <v>6.549354068576318e-08</v>
+        <v>1.362471935046403e-08</v>
       </c>
     </row>
     <row r="44">
@@ -904,10 +904,10 @@
         <v>43497</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.001070092623932559</v>
+        <v>-0.001305641235096156</v>
       </c>
       <c r="C44" t="n">
-        <v>1.145098223794869e-06</v>
+        <v>1.704699034783415e-06</v>
       </c>
     </row>
     <row r="45">
@@ -915,10 +915,10 @@
         <v>43525</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0006811111967198495</v>
+        <v>0.0009420188085527718</v>
       </c>
       <c r="C45" t="n">
-        <v>4.639124622971455e-07</v>
+        <v>8.873994356671837e-07</v>
       </c>
     </row>
     <row r="46">
@@ -926,10 +926,10 @@
         <v>43556</v>
       </c>
       <c r="B46" t="n">
-        <v>0.001458173646150155</v>
+        <v>0.001241288401447223</v>
       </c>
       <c r="C46" t="n">
-        <v>2.126270382326838e-06</v>
+        <v>1.540796895567401e-06</v>
       </c>
     </row>
     <row r="47">
@@ -937,10 +937,10 @@
         <v>43586</v>
       </c>
       <c r="B47" t="n">
-        <v>0.002206984331499154</v>
+        <v>0.002289445662676816</v>
       </c>
       <c r="C47" t="n">
-        <v>4.870779839482768e-06</v>
+        <v>5.241561442349683e-06</v>
       </c>
     </row>
     <row r="48">
@@ -948,10 +948,10 @@
         <v>43617</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.00309258182553544</v>
+        <v>-0.003338641524015589</v>
       </c>
       <c r="C48" t="n">
-        <v>9.564062347632115e-06</v>
+        <v>1.114652722588113e-05</v>
       </c>
     </row>
     <row r="49">
@@ -959,10 +959,10 @@
         <v>43647</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0002450852237267918</v>
+        <v>0.001549052212666814</v>
       </c>
       <c r="C49" t="n">
-        <v>6.006676688921159e-08</v>
+        <v>2.399562757567954e-06</v>
       </c>
     </row>
     <row r="50">
@@ -970,10 +970,10 @@
         <v>43678</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.0002012536421388109</v>
+        <v>-0.0002129489866349742</v>
       </c>
       <c r="C50" t="n">
-        <v>4.050302847413654e-08</v>
+        <v>4.53472709088624e-08</v>
       </c>
     </row>
     <row r="51">
@@ -981,10 +981,10 @@
         <v>43709</v>
       </c>
       <c r="B51" t="n">
-        <v>6.948257461802265e-05</v>
+        <v>4.059140027634097e-05</v>
       </c>
       <c r="C51" t="n">
-        <v>4.827828175549085e-09</v>
+        <v>1.647661776394134e-09</v>
       </c>
     </row>
     <row r="52">
@@ -992,10 +992,10 @@
         <v>43739</v>
       </c>
       <c r="B52" t="n">
-        <v>6.756755677894536e-05</v>
+        <v>0.0001689988345591867</v>
       </c>
       <c r="C52" t="n">
-        <v>4.565374729076005e-09</v>
+        <v>2.856060608236335e-08</v>
       </c>
     </row>
     <row r="53">
@@ -1003,10 +1003,10 @@
         <v>43770</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.001485066466767015</v>
+        <v>-0.001573661833421941</v>
       </c>
       <c r="C53" t="n">
-        <v>2.205422410715867e-06</v>
+        <v>2.476411565968906e-06</v>
       </c>
     </row>
     <row r="54">
@@ -1014,10 +1014,10 @@
         <v>43800</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0006676268565234166</v>
+        <v>0.0008155994489402612</v>
       </c>
       <c r="C54" t="n">
-        <v>4.457256195513387e-07</v>
+        <v>6.652024611116578e-07</v>
       </c>
     </row>
     <row r="55">
@@ -1025,10 +1025,10 @@
         <v>43831</v>
       </c>
       <c r="B55" t="n">
-        <v>0.001541108800287148</v>
+        <v>0.0007349785572649492</v>
       </c>
       <c r="C55" t="n">
-        <v>2.375016334322492e-06</v>
+        <v>5.401934796392662e-07</v>
       </c>
     </row>
     <row r="56">
@@ -1036,10 +1036,10 @@
         <v>43862</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.0001290870391244492</v>
+        <v>0.0003470864590558549</v>
       </c>
       <c r="C56" t="n">
-        <v>1.666346366991709e-08</v>
+        <v>1.204690100599317e-07</v>
       </c>
     </row>
     <row r="57">
@@ -1047,10 +1047,10 @@
         <v>43891</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.003449229401495084</v>
+        <v>-0.003301526584172113</v>
       </c>
       <c r="C57" t="n">
-        <v>1.189718346413813e-05</v>
+        <v>1.090007778599518e-05</v>
       </c>
     </row>
     <row r="58">
@@ -1058,10 +1058,10 @@
         <v>43922</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.005976115817181374</v>
+        <v>-0.007095430940971946</v>
       </c>
       <c r="C58" t="n">
-        <v>3.571396026036541e-05</v>
+        <v>5.034514023810204e-05</v>
       </c>
     </row>
     <row r="59">
@@ -1069,10 +1069,10 @@
         <v>43952</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.001558741307280541</v>
+        <v>-0.001297486796471072</v>
       </c>
       <c r="C59" t="n">
-        <v>2.42967446302265e-06</v>
+        <v>1.683471987016766e-06</v>
       </c>
     </row>
     <row r="60">
@@ -1080,10 +1080,10 @@
         <v>43983</v>
       </c>
       <c r="B60" t="n">
-        <v>0.002060467871223391</v>
+        <v>0.003086135525915549</v>
       </c>
       <c r="C60" t="n">
-        <v>4.245527848343853e-06</v>
+        <v>9.524232484318044e-06</v>
       </c>
     </row>
     <row r="61">
@@ -1091,10 +1091,10 @@
         <v>44013</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0003608670145176132</v>
+        <v>0.001045952350195794</v>
       </c>
       <c r="C61" t="n">
-        <v>1.302250021668552e-07</v>
+        <v>1.094016318880105e-06</v>
       </c>
     </row>
     <row r="62">
@@ -1102,10 +1102,10 @@
         <v>44044</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.0007974943896370788</v>
+        <v>-0.0005425960310603468</v>
       </c>
       <c r="C62" t="n">
-        <v>6.359973015026169e-07</v>
+        <v>2.944104529224408e-07</v>
       </c>
     </row>
     <row r="63">
@@ -1113,10 +1113,10 @@
         <v>44075</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.003380557696771028</v>
+        <v>-0.001672558126570946</v>
       </c>
       <c r="C63" t="n">
-        <v>1.142817034119784e-05</v>
+        <v>2.797450686758513e-06</v>
       </c>
     </row>
     <row r="64">
@@ -1124,10 +1124,10 @@
         <v>44105</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.000397543543178157</v>
+        <v>0.001382062087731651</v>
       </c>
       <c r="C64" t="n">
-        <v>1.580408687226431e-07</v>
+        <v>1.910095614345171e-06</v>
       </c>
     </row>
     <row r="65">
@@ -1135,10 +1135,10 @@
         <v>44136</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0006940830245452838</v>
+        <v>0.0001613264468500348</v>
       </c>
       <c r="C65" t="n">
-        <v>4.817512449619291e-07</v>
+        <v>2.602622245325711e-08</v>
       </c>
     </row>
     <row r="66">
@@ -1146,10 +1146,10 @@
         <v>44166</v>
       </c>
       <c r="B66" t="n">
-        <v>0.001656641026603334</v>
+        <v>0.001000414784567524</v>
       </c>
       <c r="C66" t="n">
-        <v>2.744459491025349e-06</v>
+        <v>1.000829741181285e-06</v>
       </c>
     </row>
     <row r="67">
@@ -1157,10 +1157,10 @@
         <v>44197</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0002075331414504863</v>
+        <v>0.0007840759623662808</v>
       </c>
       <c r="C67" t="n">
-        <v>4.307000480030757e-08</v>
+        <v>6.147751147606094e-07</v>
       </c>
     </row>
     <row r="68">
@@ -1168,10 +1168,10 @@
         <v>44228</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.003201542047717987</v>
+        <v>-0.003335128291979989</v>
       </c>
       <c r="C68" t="n">
-        <v>1.024987148330628e-05</v>
+        <v>1.112308072396536e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1179,10 +1179,10 @@
         <v>44256</v>
       </c>
       <c r="B69" t="n">
-        <v>0.00279762771696141</v>
+        <v>0.001752763100651022</v>
       </c>
       <c r="C69" t="n">
-        <v>7.826720842710708e-06</v>
+        <v>3.072178487003784e-06</v>
       </c>
     </row>
     <row r="70">
@@ -1190,10 +1190,10 @@
         <v>44287</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0037246358553477</v>
+        <v>0.00292285340767144</v>
       </c>
       <c r="C70" t="n">
-        <v>1.387291225494169e-05</v>
+        <v>8.543072042736552e-06</v>
       </c>
     </row>
     <row r="71">
@@ -1201,10 +1201,10 @@
         <v>44317</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.003686923063149986</v>
+        <v>-0.003474277520400843</v>
       </c>
       <c r="C71" t="n">
-        <v>1.359340167358728e-05</v>
+        <v>1.207060428876263e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1212,10 +1212,10 @@
         <v>44348</v>
       </c>
       <c r="B72" t="n">
-        <v>0.002287335161360047</v>
+        <v>0.001841879486291129</v>
       </c>
       <c r="C72" t="n">
-        <v>5.231902140393994e-06</v>
+        <v>3.392520042020072e-06</v>
       </c>
     </row>
     <row r="73">
@@ -1223,10 +1223,10 @@
         <v>44378</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.003047489839647306</v>
+        <v>-0.001790740298063751</v>
       </c>
       <c r="C73" t="n">
-        <v>9.287194322753561e-06</v>
+        <v>3.206750815109451e-06</v>
       </c>
     </row>
     <row r="74">
@@ -1234,10 +1234,10 @@
         <v>44409</v>
       </c>
       <c r="B74" t="n">
-        <v>0.002785048040741079</v>
+        <v>0.002105830742466923</v>
       </c>
       <c r="C74" t="n">
-        <v>7.756492589235723e-06</v>
+        <v>4.43452311591879e-06</v>
       </c>
     </row>
     <row r="75">
@@ -1245,10 +1245,10 @@
         <v>44440</v>
       </c>
       <c r="B75" t="n">
-        <v>0.004117465845808198</v>
+        <v>0.003123431072798667</v>
       </c>
       <c r="C75" t="n">
-        <v>1.695352499139702e-05</v>
+        <v>9.755821666524232e-06</v>
       </c>
     </row>
     <row r="76">
@@ -1256,10 +1256,10 @@
         <v>44470</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0009368723910517514</v>
+        <v>0.002033298262606572</v>
       </c>
       <c r="C76" t="n">
-        <v>8.777298771150257e-07</v>
+        <v>4.134301824718903e-06</v>
       </c>
     </row>
     <row r="77">
@@ -1267,10 +1267,10 @@
         <v>44501</v>
       </c>
       <c r="B77" t="n">
-        <v>0.001981131889454574</v>
+        <v>0.0021795704161104</v>
       </c>
       <c r="C77" t="n">
-        <v>3.92488356341385e-06</v>
+        <v>4.750527198783661e-06</v>
       </c>
     </row>
     <row r="78">
@@ -1278,10 +1278,10 @@
         <v>44531</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.002484298069890772</v>
+        <v>-0.002656963024259426</v>
       </c>
       <c r="C78" t="n">
-        <v>6.171736900063016e-06</v>
+        <v>7.059452512281796e-06</v>
       </c>
     </row>
     <row r="79">
@@ -1289,10 +1289,10 @@
         <v>44562</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0005526958471941332</v>
+        <v>0.0006742891124080705</v>
       </c>
       <c r="C79" t="n">
-        <v>3.054726995056406e-07</v>
+        <v>4.546658071120635e-07</v>
       </c>
     </row>
     <row r="80">
@@ -1300,10 +1300,10 @@
         <v>44593</v>
       </c>
       <c r="B80" t="n">
-        <v>0.003950404204316658</v>
+        <v>0.003364170421747477</v>
       </c>
       <c r="C80" t="n">
-        <v>1.560569337748273e-05</v>
+        <v>1.13176426265606e-05</v>
       </c>
     </row>
     <row r="81">
@@ -1311,10 +1311,10 @@
         <v>44621</v>
       </c>
       <c r="B81" t="n">
-        <v>0.001691905990813821</v>
+        <v>0.001470712159316541</v>
       </c>
       <c r="C81" t="n">
-        <v>2.862545881751697e-06</v>
+        <v>2.162994255561523e-06</v>
       </c>
     </row>
     <row r="82">
@@ -1322,10 +1322,10 @@
         <v>44652</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0004773001366089244</v>
+        <v>0.0009179807598138094</v>
       </c>
       <c r="C82" t="n">
-        <v>2.278154204068979e-07</v>
+        <v>8.426886753883389e-07</v>
       </c>
     </row>
     <row r="83">
@@ -1333,10 +1333,10 @@
         <v>44682</v>
       </c>
       <c r="B83" t="n">
-        <v>0.005715068329080788</v>
+        <v>0.005065618786638562</v>
       </c>
       <c r="C83" t="n">
-        <v>3.266200600606227e-05</v>
+        <v>2.566049369154553e-05</v>
       </c>
     </row>
     <row r="84">
@@ -1344,10 +1344,10 @@
         <v>44713</v>
       </c>
       <c r="B84" t="n">
-        <v>0.000438475683168244</v>
+        <v>0.0004998551121908842</v>
       </c>
       <c r="C84" t="n">
-        <v>1.922609247298583e-07</v>
+        <v>2.498551331833614e-07</v>
       </c>
     </row>
     <row r="85">
@@ -1355,10 +1355,10 @@
         <v>44743</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.001748628918894776</v>
+        <v>-0.000741703143377331</v>
       </c>
       <c r="C85" t="n">
-        <v>3.057703095995114e-06</v>
+        <v>5.501235528958136e-07</v>
       </c>
     </row>
     <row r="86">
@@ -1366,10 +1366,10 @@
         <v>44774</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001410086619596514</v>
+        <v>0.002411319915928963</v>
       </c>
       <c r="C86" t="n">
-        <v>1.988344274765125e-06</v>
+        <v>5.814463736955662e-06</v>
       </c>
     </row>
     <row r="87">
@@ -1377,10 +1377,10 @@
         <v>44805</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0009617319576199035</v>
+        <v>-0.00203278259043237</v>
       </c>
       <c r="C87" t="n">
-        <v>9.249283583074119e-07</v>
+        <v>4.132205059964936e-06</v>
       </c>
     </row>
     <row r="88">
@@ -1388,10 +1388,10 @@
         <v>44835</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.0001371198150129534</v>
+        <v>0.0004118306142798609</v>
       </c>
       <c r="C88" t="n">
-        <v>1.880184366918656e-08</v>
+        <v>1.696044548581276e-07</v>
       </c>
     </row>
     <row r="89">
@@ -1399,10 +1399,10 @@
         <v>44866</v>
       </c>
       <c r="B89" t="n">
-        <v>1.132214982451697e-05</v>
+        <v>0.0002682733737944385</v>
       </c>
       <c r="C89" t="n">
-        <v>1.281910766488096e-10</v>
+        <v>7.197060308705053e-08</v>
       </c>
     </row>
     <row r="90">
@@ -1410,10 +1410,10 @@
         <v>44896</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.0007686042374776233</v>
+        <v>-0.00106111648705281</v>
       </c>
       <c r="C90" t="n">
-        <v>5.907524738685587e-07</v>
+        <v>1.125968199095297e-06</v>
       </c>
     </row>
     <row r="91">
@@ -1421,10 +1421,10 @@
         <v>44927</v>
       </c>
       <c r="B91" t="n">
-        <v>-8.796141836638961e-05</v>
+        <v>0.0004947594151153352</v>
       </c>
       <c r="C91" t="n">
-        <v>7.737211121027023e-09</v>
+        <v>2.447868788452686e-07</v>
       </c>
     </row>
     <row r="92">
@@ -1432,10 +1432,10 @@
         <v>44958</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.0005553085586622736</v>
+        <v>-0.0003481999496051172</v>
       </c>
       <c r="C92" t="n">
-        <v>3.083675953235717e-07</v>
+        <v>1.212432049050062e-07</v>
       </c>
     </row>
     <row r="93">
@@ -1443,10 +1443,10 @@
         <v>44986</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.0005310705633002066</v>
+        <v>-0.001470384269728651</v>
       </c>
       <c r="C93" t="n">
-        <v>2.820359432039988e-07</v>
+        <v>2.162029900665459e-06</v>
       </c>
     </row>
     <row r="94">
@@ -1454,10 +1454,10 @@
         <v>45017</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.001860606886835403</v>
+        <v>-0.001371705088544817</v>
       </c>
       <c r="C94" t="n">
-        <v>3.461857987339331e-06</v>
+        <v>1.881574849939744e-06</v>
       </c>
     </row>
     <row r="95">
@@ -1465,10 +1465,10 @@
         <v>45047</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.002961059102060175</v>
+        <v>-0.003184599925566218</v>
       </c>
       <c r="C95" t="n">
-        <v>8.767871005893408e-06</v>
+        <v>1.014167668591636e-05</v>
       </c>
     </row>
     <row r="96">
@@ -1476,10 +1476,10 @@
         <v>45078</v>
       </c>
       <c r="B96" t="n">
-        <v>0.001578103583485316</v>
+        <v>0.001113351865493767</v>
       </c>
       <c r="C96" t="n">
-        <v>2.490410920209197e-06</v>
+        <v>1.23955237639845e-06</v>
       </c>
     </row>
     <row r="97">
@@ -1487,10 +1487,10 @@
         <v>45108</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.0004435331517692386</v>
+        <v>-0.0006525893334285392</v>
       </c>
       <c r="C97" t="n">
-        <v>1.967216567183545e-07</v>
+        <v>4.258728381047051e-07</v>
       </c>
     </row>
     <row r="98">
@@ -1498,10 +1498,10 @@
         <v>45139</v>
       </c>
       <c r="B98" t="n">
-        <v>0.002873733769275469</v>
+        <v>0.002475439330445184</v>
       </c>
       <c r="C98" t="n">
-        <v>8.258345776674194e-06</v>
+        <v>6.127799878714899e-06</v>
       </c>
     </row>
     <row r="99">
@@ -1509,10 +1509,10 @@
         <v>45170</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.003348134884382972</v>
+        <v>-0.003673451893294465</v>
       </c>
       <c r="C99" t="n">
-        <v>1.121000720402218e-05</v>
+        <v>1.349424881234869e-05</v>
       </c>
     </row>
     <row r="100">
@@ -1520,10 +1520,10 @@
         <v>45200</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.0006432387642667079</v>
+        <v>-0.001063397183191066</v>
       </c>
       <c r="C100" t="n">
-        <v>4.137561078553615e-07</v>
+        <v>1.130813569218693e-06</v>
       </c>
     </row>
     <row r="101">
@@ -1531,10 +1531,10 @@
         <v>45231</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.002259090104947566</v>
+        <v>-0.002352994022683926</v>
       </c>
       <c r="C101" t="n">
-        <v>5.103488102272007e-06</v>
+        <v>5.536580870786283e-06</v>
       </c>
     </row>
     <row r="102">
@@ -1542,10 +1542,10 @@
         <v>45261</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.0007452439396048892</v>
+        <v>-0.001266412433604385</v>
       </c>
       <c r="C102" t="n">
-        <v>5.553885295178157e-07</v>
+        <v>1.60380045198778e-06</v>
       </c>
     </row>
     <row r="103">
@@ -1553,10 +1553,10 @@
         <v>45292</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0002236734993403697</v>
+        <v>0.0003057476424372913</v>
       </c>
       <c r="C103" t="n">
-        <v>5.002983430716637e-08</v>
+        <v>9.348162085596172e-08</v>
       </c>
     </row>
     <row r="104">
@@ -1564,10 +1564,10 @@
         <v>45323</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0008944969830093548</v>
+        <v>0.0005579880637677985</v>
       </c>
       <c r="C104" t="n">
-        <v>8.001248526128381e-07</v>
+        <v>3.113506793073368e-07</v>
       </c>
     </row>
     <row r="105">
@@ -1575,10 +1575,10 @@
         <v>45352</v>
       </c>
       <c r="B105" t="n">
-        <v>0.0007858866398589203</v>
+        <v>0.001082021907062809</v>
       </c>
       <c r="C105" t="n">
-        <v>6.176178107087443e-07</v>
+        <v>1.170771407363839e-06</v>
       </c>
     </row>
     <row r="106">
@@ -1586,10 +1586,10 @@
         <v>45383</v>
       </c>
       <c r="B106" t="n">
-        <v>0.007113295565447614</v>
+        <v>0.006645180732503928</v>
       </c>
       <c r="C106" t="n">
-        <v>5.05989738014167e-05</v>
+        <v>4.415842696764144e-05</v>
       </c>
     </row>
     <row r="107">
@@ -1597,10 +1597,10 @@
         <v>45413</v>
       </c>
       <c r="B107" t="n">
-        <v>0.001141404966667878</v>
+        <v>0.001012036426134502</v>
       </c>
       <c r="C107" t="n">
-        <v>1.302805297934101e-06</v>
+        <v>1.024217727823096e-06</v>
       </c>
     </row>
     <row r="108">
@@ -1608,10 +1608,10 @@
         <v>45444</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.001395776747433092</v>
+        <v>-0.0009559886478763245</v>
       </c>
       <c r="C108" t="n">
-        <v>1.948192728674902e-06</v>
+        <v>9.139142948684031e-07</v>
       </c>
     </row>
     <row r="109">
@@ -1619,10 +1619,10 @@
         <v>45474</v>
       </c>
       <c r="B109" t="n">
-        <v>0.001385046236325568</v>
+        <v>0.002211960061141364</v>
       </c>
       <c r="C109" t="n">
-        <v>1.91835307675962e-06</v>
+        <v>4.892767312084506e-06</v>
       </c>
     </row>
     <row r="110">
@@ -1630,10 +1630,10 @@
         <v>45505</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0006022025100035935</v>
+        <v>0.0002821154048614933</v>
       </c>
       <c r="C110" t="n">
-        <v>3.626478630546282e-07</v>
+        <v>7.958910166016427e-08</v>
       </c>
     </row>
     <row r="111">
@@ -1641,10 +1641,10 @@
         <v>45536</v>
       </c>
       <c r="B111" t="n">
-        <v>-0.005249806926437606</v>
+        <v>-0.005535405578786347</v>
       </c>
       <c r="C111" t="n">
-        <v>2.756047276487227e-05</v>
+        <v>3.064071492165901e-05</v>
       </c>
     </row>
     <row r="112">
@@ -1652,10 +1652,10 @@
         <v>45566</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.0001891754079720292</v>
+        <v>0.0003668382559249357</v>
       </c>
       <c r="C112" t="n">
-        <v>3.578733498138368e-08</v>
+        <v>1.345703060100486e-07</v>
       </c>
     </row>
     <row r="113">
@@ -1663,10 +1663,10 @@
         <v>45597</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.0008751976053282441</v>
+        <v>-0.00215500166133656</v>
       </c>
       <c r="C113" t="n">
-        <v>7.65970848372293e-07</v>
+        <v>4.644032160363335e-06</v>
       </c>
     </row>
     <row r="114">
@@ -1674,10 +1674,10 @@
         <v>45627</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.000523608449890085</v>
+        <v>-0.0005680121183312477</v>
       </c>
       <c r="C114" t="n">
-        <v>2.741658087962976e-07</v>
+        <v>3.226377665711513e-07</v>
       </c>
     </row>
     <row r="115">
@@ -1685,10 +1685,10 @@
         <v>45658</v>
       </c>
       <c r="B115" t="n">
-        <v>0.001124039476808655</v>
+        <v>0.001230223841789749</v>
       </c>
       <c r="C115" t="n">
-        <v>1.263464745424276e-06</v>
+        <v>1.513450700907929e-06</v>
       </c>
     </row>
     <row r="116">
@@ -1696,10 +1696,10 @@
         <v>45689</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.001867315035853803</v>
+        <v>-0.002727986054483532</v>
       </c>
       <c r="C116" t="n">
-        <v>3.486865443125691e-06</v>
+        <v>7.441907913456627e-06</v>
       </c>
     </row>
   </sheetData>
